--- a/AAII_Financials/Quarterly/CLWT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CLWT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="92">
   <si>
     <t>CLWT</t>
   </si>
@@ -1059,10 +1059,10 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>-800</v>
+        <v>1200</v>
       </c>
       <c r="E12" s="3">
-        <v>-800</v>
+        <v>1200</v>
       </c>
       <c r="F12" s="3">
         <v>1100</v>
@@ -3260,10 +3260,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="E43" s="3">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="F43" s="3">
         <v>1600</v>
@@ -3425,11 +3425,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -4484,10 +4484,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="E59" s="3">
-        <v>1700</v>
+        <v>700</v>
       </c>
       <c r="F59" s="3">
         <v>700</v>
